--- a/resources/templates/karaba/deregistration_contract.xlsx
+++ b/resources/templates/karaba/deregistration_contract.xlsx
@@ -443,7 +443,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">SELLER : SUNGSIN MOTORS CO.LTD</t>
+      <t xml:space="preserve">SELLER : KARABA CO., LTD</t>
     </r>
   </si>
   <si>
@@ -1263,7 +1263,7 @@
     <col min="20" max="20" width="9" customWidth="true" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16134" customHeight="1" ht="38.25" s="36" customFormat="1">
+    <row r="1" spans="1:20" customHeight="1" ht="38.25" s="36" customFormat="1">
       <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="2" spans="1:16134" customHeight="1" ht="11.25" s="36" customFormat="1">
+    <row r="2" spans="1:20" customHeight="1" ht="11.25" s="36" customFormat="1">
       <c r="A2" s="33" t="inlineStr">
         <is>
           <r>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
     </row>
-    <row r="3" spans="1:16134" customHeight="1" ht="15.75" s="36" customFormat="1">
+    <row r="3" spans="1:20" customHeight="1" ht="15.75" s="36" customFormat="1">
       <c r="A3" s="33" t="inlineStr">
         <is>
           <r>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
     </row>
-    <row r="4" spans="1:16134" customHeight="1" ht="13.7" s="36" customFormat="1">
+    <row r="4" spans="1:20" customHeight="1" ht="13.7" s="36" customFormat="1">
       <c r="A4" s="2"/>
       <c r="B4" s="3"/>
       <c r="C4" s="4"/>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
     </row>
-    <row r="5" spans="1:16134" customHeight="1" ht="14.25" s="36" customFormat="1">
+    <row r="5" spans="1:20" customHeight="1" ht="14.25" s="36" customFormat="1">
       <c r="A5" s="2"/>
       <c r="B5" s="3"/>
       <c r="C5" s="4"/>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
     </row>
-    <row r="6" spans="1:16134" customHeight="1" ht="18.75" s="36" customFormat="1">
+    <row r="6" spans="1:20" customHeight="1" ht="18.75" s="36" customFormat="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
           <r>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
     </row>
-    <row r="7" spans="1:16134">
+    <row r="7" spans="1:20">
       <c r="A7" s="28" t="inlineStr">
         <is>
           <r>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
     </row>
-    <row r="8" spans="1:16134">
+    <row r="8" spans="1:20">
       <c r="A8" s="28" t="inlineStr">
         <is>
           <r>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
     </row>
-    <row r="9" spans="1:16134">
+    <row r="9" spans="1:20">
       <c r="A9" s="28" t="inlineStr">
         <is>
           <r>
@@ -1358,8 +1358,8 @@
         </is>
       </c>
     </row>
-    <row r="10" spans="1:16134" customHeight="1" ht="6.75" s="36" customFormat="1"/>
-    <row r="11" spans="1:16134" customHeight="1" ht="11.25" s="36" customFormat="1">
+    <row r="10" spans="1:20" customHeight="1" ht="6.75" s="36" customFormat="1"/>
+    <row r="11" spans="1:20" customHeight="1" ht="11.25" s="36" customFormat="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <r>
@@ -1389,7 +1389,7 @@
         </is>
       </c>
     </row>
-    <row r="12" spans="1:16134" customHeight="1" ht="11.25" s="36" customFormat="1">
+    <row r="12" spans="1:20" customHeight="1" ht="11.25" s="36" customFormat="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <r>
@@ -1407,7 +1407,7 @@
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
     </row>
-    <row r="13" spans="1:16134" customHeight="1" ht="11.25" s="36" customFormat="1">
+    <row r="13" spans="1:20" customHeight="1" ht="11.25" s="36" customFormat="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <r>
@@ -1426,7 +1426,7 @@
       <c r="D13" s="9"/>
       <c r="E13" s="7"/>
     </row>
-    <row r="14" spans="1:16134" customHeight="1" ht="11.25" s="36" customFormat="1">
+    <row r="14" spans="1:20" customHeight="1" ht="11.25" s="36" customFormat="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <r>
@@ -1445,7 +1445,7 @@
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
     </row>
-    <row r="15" spans="1:16134" customHeight="1" ht="11.25" s="36" customFormat="1">
+    <row r="15" spans="1:20" customHeight="1" ht="11.25" s="36" customFormat="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <r>
@@ -1464,7 +1464,7 @@
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
     </row>
-    <row r="16" spans="1:16134" customHeight="1" ht="11.25" s="36" customFormat="1">
+    <row r="16" spans="1:20" customHeight="1" ht="11.25" s="36" customFormat="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <r>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
     </row>
-    <row r="17" spans="1:16134">
+    <row r="17" spans="1:20">
       <c r="A17" s="10" t="inlineStr">
         <is>
           <r>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
     </row>
-    <row r="18" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="18" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A18" s="13" t="inlineStr">
         <is>
           <r>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
     </row>
-    <row r="19" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="19" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
           <r>
@@ -1604,7 +1604,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="20" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="20" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A20" s="13" t="inlineStr">
         <is>
           <r>
@@ -1633,7 +1633,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="21" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="21" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A21" s="13" t="inlineStr">
         <is>
           <r>
@@ -1662,7 +1662,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="22" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="22" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A22" s="13" t="inlineStr">
         <is>
           <r>
@@ -1691,7 +1691,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="23" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="23" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A23" s="13" t="inlineStr">
         <is>
           <r>
@@ -1720,7 +1720,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="24" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="24" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A24" s="13" t="inlineStr">
         <is>
           <r>
@@ -1749,7 +1749,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="25" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="25" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A25" s="13" t="inlineStr">
         <is>
           <r>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
     </row>
-    <row r="26" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="26" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A26" s="13" t="inlineStr">
         <is>
           <r>
@@ -1814,7 +1814,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="27" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="27" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A27" s="13" t="inlineStr">
         <is>
           <r>
@@ -1843,7 +1843,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="28" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="28" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A28" s="13" t="inlineStr">
         <is>
           <r>
@@ -1872,7 +1872,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="29" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="29" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A29" s="13" t="inlineStr">
         <is>
           <r>
@@ -1901,7 +1901,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="30" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="30" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A30" s="13" t="inlineStr">
         <is>
           <r>
@@ -1930,7 +1930,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="31" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="31" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A31" s="13" t="inlineStr">
         <is>
           <r>
@@ -1959,7 +1959,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="32" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="32" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A32" s="13" t="inlineStr">
         <is>
           <r>
@@ -1988,7 +1988,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="33" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="33" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A33" s="13" t="inlineStr">
         <is>
           <r>
@@ -2017,7 +2017,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="34" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="34" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A34" s="13" t="inlineStr">
         <is>
           <r>
@@ -2046,7 +2046,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="35" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="35" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
           <r>
@@ -2075,7 +2075,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="36" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="36" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A36" s="13" t="inlineStr">
         <is>
           <r>
@@ -2104,7 +2104,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="37" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="37" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A37" s="13" t="inlineStr">
         <is>
           <r>
@@ -2133,7 +2133,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="38" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="38" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A38" s="13" t="inlineStr">
         <is>
           <r>
@@ -2162,7 +2162,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="39" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="39" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A39" s="13" t="inlineStr">
         <is>
           <r>
@@ -2191,7 +2191,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="40" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="40" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A40" s="13" t="inlineStr">
         <is>
           <r>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
     </row>
-    <row r="41" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="41" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A41" s="13" t="inlineStr">
         <is>
           <r>
@@ -2256,7 +2256,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="42" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="42" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A42" s="13" t="inlineStr">
         <is>
           <r>
@@ -2285,7 +2285,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="43" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="43" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A43" s="13" t="inlineStr">
         <is>
           <r>
@@ -2314,7 +2314,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="44" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="44" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A44" s="13" t="inlineStr">
         <is>
           <r>
@@ -2343,7 +2343,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="45" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="45" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A45" s="13" t="inlineStr">
         <is>
           <r>
@@ -2372,7 +2372,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="46" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="46" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A46" s="13" t="inlineStr">
         <is>
           <r>
@@ -2401,7 +2401,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="47" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="47" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A47" s="13" t="inlineStr">
         <is>
           <r>
@@ -2430,7 +2430,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="48" spans="1:16134" customHeight="1" ht="12.75" s="36" customFormat="1">
+    <row r="48" spans="1:20" customHeight="1" ht="12.75" s="36" customFormat="1">
       <c r="A48" s="13" t="inlineStr">
         <is>
           <r>
@@ -2459,7 +2459,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="49" spans="1:16134" customHeight="1" ht="16.5" s="36" customFormat="1">
+    <row r="49" spans="1:20" customHeight="1" ht="16.5" s="36" customFormat="1">
       <c r="A49" s="30" t="inlineStr">
         <is>
           <r>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E49" s="39"/>
     </row>
-    <row r="50" spans="1:16134" customHeight="1" ht="18.75" s="36" customFormat="1">
+    <row r="50" spans="1:20" customHeight="1" ht="18.75" s="36" customFormat="1">
       <c r="A50" s="15" t="inlineStr">
         <is>
           <r>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="E50" s="43"/>
     </row>
-    <row r="51" spans="1:16134" customHeight="1" ht="12.75" s="16" customFormat="1">
+    <row r="51" spans="1:20" customHeight="1" ht="12.75" s="16" customFormat="1">
       <c r="A51" s="16" t="inlineStr">
         <is>
           <r>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
     </row>
-    <row r="52" spans="1:16134" customHeight="1" ht="12.75" s="16" customFormat="1">
+    <row r="52" spans="1:20" customHeight="1" ht="12.75" s="16" customFormat="1">
       <c r="A52" s="16" t="inlineStr">
         <is>
           <r>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
     </row>
-    <row r="53" spans="1:16134" customHeight="1" ht="12.75" s="16" customFormat="1">
+    <row r="53" spans="1:20" customHeight="1" ht="12.75" s="16" customFormat="1">
       <c r="A53" s="16" t="inlineStr">
         <is>
           <r>
@@ -2540,8 +2540,8 @@
         </is>
       </c>
     </row>
-    <row r="54" spans="1:16134" customHeight="1" ht="6" s="16" customFormat="1"/>
-    <row r="55" spans="1:16134">
+    <row r="54" spans="1:20" customHeight="1" ht="6" s="16" customFormat="1"/>
+    <row r="55" spans="1:20">
       <c r="A55" s="17" t="inlineStr">
         <is>
           <r>
@@ -2562,14 +2562,14 @@
         </is>
       </c>
     </row>
-    <row r="56" spans="1:16134" customHeight="1" ht="3.75" s="36" customFormat="1">
+    <row r="56" spans="1:20" customHeight="1" ht="3.75" s="36" customFormat="1">
       <c r="A56" s="20"/>
       <c r="B56" s="21"/>
       <c r="C56" s="22"/>
       <c r="D56" s="23"/>
       <c r="E56" s="24"/>
     </row>
-    <row r="57" spans="1:16134" customHeight="1" ht="20.25" s="36" customFormat="1">
+    <row r="57" spans="1:20" customHeight="1" ht="20.25" s="36" customFormat="1">
       <c r="A57" s="26" t="inlineStr">
         <is>
           <r>
@@ -2580,12 +2580,12 @@
       <c r="C57" s="26" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">SELLER : SUNGSIN MOTORS CO.LTD</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="58" spans="1:16134" customHeight="1" ht="18.75" s="36" customFormat="1">
+            <t xml:space="preserve">SELLER : KARABA CO., LTD</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="58" spans="1:20" customHeight="1" ht="18.75" s="36" customFormat="1">
       <c r="A58" s="27" t="inlineStr">
         <is>
           <r>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
     </row>
-    <row r="59" spans="1:16134" customHeight="1" ht="11.25" s="36" customFormat="1">
+    <row r="59" spans="1:20" customHeight="1" ht="11.25" s="36" customFormat="1">
       <c r="A59" s="1" t="inlineStr">
         <is>
           <r>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
     </row>
-    <row r="60" spans="1:16134" customHeight="1" ht="11.25" s="36" customFormat="1">
+    <row r="60" spans="1:20" customHeight="1" ht="11.25" s="36" customFormat="1">
       <c r="A60" s="36"/>
     </row>
-    <row r="61" spans="1:16134" customHeight="1" ht="3.75" s="36" customFormat="1">
+    <row r="61" spans="1:20" customHeight="1" ht="3.75" s="36" customFormat="1">
       <c r="A61" s="25"/>
       <c r="B61" s="25"/>
       <c r="C61" s="25"/>

--- a/resources/templates/karaba/deregistration_contract.xlsx
+++ b/resources/templates/karaba/deregistration_contract.xlsx
@@ -33,7 +33,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">TEL : 82 -10-9009-9977</t>
+      <t xml:space="preserve">TEL : 82-32-710-7979</t>
     </r>
   </si>
   <si>
@@ -1297,7 +1297,7 @@
       <c r="E4" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">TEL : 82 -10-9009-9977</t>
+            <t xml:space="preserve">TEL : 82-32-710-7979</t>
           </r>
         </is>
       </c>

--- a/resources/templates/karaba/deregistration_contract.xlsx
+++ b/resources/templates/karaba/deregistration_contract.xlsx
@@ -37,9 +37,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">FAX : 82 - 031 - 499 - 1989</t>
-    </r>
+    <t>FAX : 82-32-710-1881</t>
   </si>
   <si>
     <r>
@@ -1307,12 +1305,8 @@
       <c r="B5" s="3"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">FAX : 82 - 031 - 499 - 1989</t>
-          </r>
-        </is>
+      <c r="E5" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="G5" s="34" t="inlineStr">
         <is>
